--- a/sheets/조재수대금교본/검수/뽕따러가세.xlsx
+++ b/sheets/조재수대금교본/검수/뽕따러가세.xlsx
@@ -3070,11 +3070,7 @@
         </is>
       </c>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
@@ -3176,45 +3172,31 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ㅂ
-‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
     <row r="9" ht="90.2" customHeight="true">
@@ -3234,7 +3216,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ
+          <t xml:space="preserve">湳
 △</t>
         </is>
       </c>
@@ -3242,7 +3224,6 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 –汰</t>
         </is>
       </c>
@@ -3266,7 +3247,6 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 –林</t>
         </is>
       </c>
@@ -3274,7 +3254,6 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 –汰</t>
         </is>
       </c>
@@ -3302,7 +3281,6 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 –汰</t>
         </is>
       </c>
@@ -3322,17 +3300,9 @@
         </is>
       </c>
       <c r="E11" s="24"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F11" s="21"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
@@ -3371,7 +3341,6 @@
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-ﾉ
 –汰</t>
         </is>
       </c>
@@ -3435,22 +3404,13 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I14" s="24"/>

--- a/sheets/조재수대금교본/검수/뽕따러가세.xlsx
+++ b/sheets/조재수대금교본/검수/뽕따러가세.xlsx
@@ -3182,11 +3182,16 @@
         </is>
       </c>
       <c r="E8" s="24"/>
-      <c r="F8" s="21"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅂ</t>
+        </is>
+      </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -3216,7 +3221,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳ㄴ
 △</t>
         </is>
       </c>
@@ -3224,6 +3229,7 @@
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 –汰</t>
         </is>
       </c>
@@ -3247,6 +3253,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 –林</t>
         </is>
       </c>
@@ -3254,6 +3261,7 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 –汰</t>
         </is>
       </c>
@@ -3281,6 +3289,7 @@
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 –汰</t>
         </is>
       </c>
@@ -3341,6 +3350,7 @@
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
+ﾉ
 –汰</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/뽕따러가세.xlsx
+++ b/sheets/조재수대금교본/검수/뽕따러가세.xlsx
@@ -2946,17 +2946,17 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
